--- a/data/CVexamples.xlsx
+++ b/data/CVexamples.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devan.mcgranahan\GithubProjects\MeasuringHeterogeneity\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devan.mcgranahan\GitHubProjects\MeasuringHeterogeneity\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B760671-DF92-4513-AA03-F35BFED59F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E59D3F-0237-48D4-916C-219C07AB9123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13875" activeTab="1" xr2:uid="{AD1C4217-E13C-46B4-9D4C-332639410110}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{AD1C4217-E13C-46B4-9D4C-332639410110}"/>
   </bookViews>
   <sheets>
     <sheet name="cain1999" sheetId="1" r:id="rId1"/>
     <sheet name="turner2011" sheetId="2" r:id="rId2"/>
+    <sheet name="fuhlendorf1999" sheetId="3" r:id="rId3"/>
+    <sheet name="BronikowskiAltmann1996" sheetId="4" r:id="rId4"/>
+    <sheet name="Golodets2013" sheetId="5" r:id="rId5"/>
+    <sheet name="Dörgeloh2002a" sheetId="6" r:id="rId6"/>
+    <sheet name="Dörgeloh2002b" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="296">
   <si>
     <t>species</t>
   </si>
@@ -101,14 +106,853 @@
   </si>
   <si>
     <t>soil</t>
+  </si>
+  <si>
+    <t>1949, 1443</t>
+  </si>
+  <si>
+    <t>1950, 1032</t>
+  </si>
+  <si>
+    <t>1951, 1135</t>
+  </si>
+  <si>
+    <t>1953, 96</t>
+  </si>
+  <si>
+    <t>1955, 653</t>
+  </si>
+  <si>
+    <t>1956, 316</t>
+  </si>
+  <si>
+    <t>1957, 329</t>
+  </si>
+  <si>
+    <t>1958, 616</t>
+  </si>
+  <si>
+    <t>1959, 1229</t>
+  </si>
+  <si>
+    <t>1960, 1076</t>
+  </si>
+  <si>
+    <t>1961, 1026</t>
+  </si>
+  <si>
+    <t>1962, 444</t>
+  </si>
+  <si>
+    <t>1963, 295</t>
+  </si>
+  <si>
+    <t>1964, 505</t>
+  </si>
+  <si>
+    <t>1968, 1068</t>
+  </si>
+  <si>
+    <t>1982, 1279</t>
+  </si>
+  <si>
+    <t>1984, 402</t>
+  </si>
+  <si>
+    <t>1987, 864</t>
+  </si>
+  <si>
+    <t>1992, 535</t>
+  </si>
+  <si>
+    <t>1993, 234</t>
+  </si>
+  <si>
+    <t>grazing</t>
+  </si>
+  <si>
+    <t>YearBA</t>
+  </si>
+  <si>
+    <t>Heavy</t>
+  </si>
+  <si>
+    <t>1949, 961</t>
+  </si>
+  <si>
+    <t>1950, 831</t>
+  </si>
+  <si>
+    <t>1951, 926</t>
+  </si>
+  <si>
+    <t>1952, 653</t>
+  </si>
+  <si>
+    <t>1953, 74</t>
+  </si>
+  <si>
+    <t>1955, 571</t>
+  </si>
+  <si>
+    <t>1956, 461</t>
+  </si>
+  <si>
+    <t>1957, 486</t>
+  </si>
+  <si>
+    <t>1958, 776</t>
+  </si>
+  <si>
+    <t>1959, 1087</t>
+  </si>
+  <si>
+    <t>1960, 1210</t>
+  </si>
+  <si>
+    <t>1961, 1045</t>
+  </si>
+  <si>
+    <t>1962, 615</t>
+  </si>
+  <si>
+    <t>1963, 464</t>
+  </si>
+  <si>
+    <t>1964, 647</t>
+  </si>
+  <si>
+    <t>1968, 1131</t>
+  </si>
+  <si>
+    <t>1982, 1437</t>
+  </si>
+  <si>
+    <t>1984, 333</t>
+  </si>
+  <si>
+    <t>1987, 1065</t>
+  </si>
+  <si>
+    <t>1992, 563</t>
+  </si>
+  <si>
+    <t>1993, 418</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>1952, 599</t>
+  </si>
+  <si>
+    <t>1953, 102</t>
+  </si>
+  <si>
+    <t>1949, 753</t>
+  </si>
+  <si>
+    <t>1950, 617</t>
+  </si>
+  <si>
+    <t>1951, 619</t>
+  </si>
+  <si>
+    <t>1952, 619</t>
+  </si>
+  <si>
+    <t>1954, 212</t>
+  </si>
+  <si>
+    <t>1955, 484</t>
+  </si>
+  <si>
+    <t>1956, 368</t>
+  </si>
+  <si>
+    <t>1957, 422</t>
+  </si>
+  <si>
+    <t>1958, 454</t>
+  </si>
+  <si>
+    <t>1959, 691</t>
+  </si>
+  <si>
+    <t>1960, 726</t>
+  </si>
+  <si>
+    <t>1961, 736</t>
+  </si>
+  <si>
+    <t>1962, 373</t>
+  </si>
+  <si>
+    <t>1963, 284</t>
+  </si>
+  <si>
+    <t>1964, 224</t>
+  </si>
+  <si>
+    <t>1968, 575</t>
+  </si>
+  <si>
+    <t>1982, 318</t>
+  </si>
+  <si>
+    <t>1984, 76</t>
+  </si>
+  <si>
+    <t>1985, 99</t>
+  </si>
+  <si>
+    <t>1987, 507</t>
+  </si>
+  <si>
+    <t>1992, 180</t>
+  </si>
+  <si>
+    <t>Ungrazed</t>
+  </si>
+  <si>
+    <t>1954, 234</t>
+  </si>
+  <si>
+    <t>1954, 284</t>
+  </si>
+  <si>
+    <t>1949, 67</t>
+  </si>
+  <si>
+    <t>1950, 63</t>
+  </si>
+  <si>
+    <t>1951, 70</t>
+  </si>
+  <si>
+    <t>1952, 87</t>
+  </si>
+  <si>
+    <t>1953, 136</t>
+  </si>
+  <si>
+    <t>1954, 121</t>
+  </si>
+  <si>
+    <t>1955, 72</t>
+  </si>
+  <si>
+    <t>1956, 89</t>
+  </si>
+  <si>
+    <t>1957, 130</t>
+  </si>
+  <si>
+    <t>1958, 83</t>
+  </si>
+  <si>
+    <t>1959, 78</t>
+  </si>
+  <si>
+    <t>1960, 75</t>
+  </si>
+  <si>
+    <t>1961, 87</t>
+  </si>
+  <si>
+    <t>1962, 107</t>
+  </si>
+  <si>
+    <t>1963, 93</t>
+  </si>
+  <si>
+    <t>1964, 99</t>
+  </si>
+  <si>
+    <t>1968, 68</t>
+  </si>
+  <si>
+    <t>1982, 80</t>
+  </si>
+  <si>
+    <t>1984, 169</t>
+  </si>
+  <si>
+    <t>1987, 200</t>
+  </si>
+  <si>
+    <t>1992, 142</t>
+  </si>
+  <si>
+    <t>1993, 155</t>
+  </si>
+  <si>
+    <t>YearCV</t>
+  </si>
+  <si>
+    <t>1949, 52</t>
+  </si>
+  <si>
+    <t>1950, 81</t>
+  </si>
+  <si>
+    <t>1951, 82</t>
+  </si>
+  <si>
+    <t>1952, 97</t>
+  </si>
+  <si>
+    <t>1953, 205</t>
+  </si>
+  <si>
+    <t>1954, 140</t>
+  </si>
+  <si>
+    <t>1955, 105</t>
+  </si>
+  <si>
+    <t>1956, 102</t>
+  </si>
+  <si>
+    <t>1957, 114</t>
+  </si>
+  <si>
+    <t>1958, 94</t>
+  </si>
+  <si>
+    <t>1959, 86</t>
+  </si>
+  <si>
+    <t>1960, 94</t>
+  </si>
+  <si>
+    <t>1961, 98</t>
+  </si>
+  <si>
+    <t>1962, 126</t>
+  </si>
+  <si>
+    <t>1963, 126</t>
+  </si>
+  <si>
+    <t>1964, 122</t>
+  </si>
+  <si>
+    <t>1968, 73</t>
+  </si>
+  <si>
+    <t>1982, 84</t>
+  </si>
+  <si>
+    <t>1984, 320</t>
+  </si>
+  <si>
+    <t>1987, 264</t>
+  </si>
+  <si>
+    <t>1992, 233</t>
+  </si>
+  <si>
+    <t>1993, 158</t>
+  </si>
+  <si>
+    <t>1949, 48</t>
+  </si>
+  <si>
+    <t>1950, 84</t>
+  </si>
+  <si>
+    <t>1951, 84</t>
+  </si>
+  <si>
+    <t>1953, 195</t>
+  </si>
+  <si>
+    <t>1954, 145</t>
+  </si>
+  <si>
+    <t>1955, 97</t>
+  </si>
+  <si>
+    <t>1956, 134</t>
+  </si>
+  <si>
+    <t>1957, 136</t>
+  </si>
+  <si>
+    <t>1958, 111</t>
+  </si>
+  <si>
+    <t>1959, 102</t>
+  </si>
+  <si>
+    <t>1960, 99</t>
+  </si>
+  <si>
+    <t>1961, 105</t>
+  </si>
+  <si>
+    <t>1962, 167</t>
+  </si>
+  <si>
+    <t>1963, 158</t>
+  </si>
+  <si>
+    <t>1964, 172</t>
+  </si>
+  <si>
+    <t>1968, 121</t>
+  </si>
+  <si>
+    <t>1982, 133</t>
+  </si>
+  <si>
+    <t>1984, 237</t>
+  </si>
+  <si>
+    <t>1985, 230</t>
+  </si>
+  <si>
+    <t>1987, 485</t>
+  </si>
+  <si>
+    <t>1992, 329</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>mm_ANPP</t>
+  </si>
+  <si>
+    <t>Sede Boqer</t>
+  </si>
+  <si>
+    <t>50.4, 0.8</t>
+  </si>
+  <si>
+    <t>58.7, 1.4</t>
+  </si>
+  <si>
+    <t>64.6, 6.6</t>
+  </si>
+  <si>
+    <t>81.9, 3.7</t>
+  </si>
+  <si>
+    <t>84.5, 9.5</t>
+  </si>
+  <si>
+    <t>73.0, 16.3</t>
+  </si>
+  <si>
+    <t>159.7, 14.4</t>
+  </si>
+  <si>
+    <t>178.4, 45.4</t>
+  </si>
+  <si>
+    <t>57.0, 0</t>
+  </si>
+  <si>
+    <t>72.4, 9.4</t>
+  </si>
+  <si>
+    <t>106.6, 44.4</t>
+  </si>
+  <si>
+    <t>101.3, 61.0</t>
+  </si>
+  <si>
+    <t>127.6, 61.1</t>
+  </si>
+  <si>
+    <t>148.7, 79.4</t>
+  </si>
+  <si>
+    <t>156.6, 102.1</t>
+  </si>
+  <si>
+    <t>160.5, 71.9</t>
+  </si>
+  <si>
+    <t>178.9, 62.9</t>
+  </si>
+  <si>
+    <t>201.3, 64.5</t>
+  </si>
+  <si>
+    <t>178.9, 87.1</t>
+  </si>
+  <si>
+    <t>289.5, 249.5</t>
+  </si>
+  <si>
+    <t>Shaked Park</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Lehavim</t>
+  </si>
+  <si>
+    <t>141.7, 20.6</t>
+  </si>
+  <si>
+    <t>163.5, 45.3</t>
+  </si>
+  <si>
+    <t>171.5, 60.1</t>
+  </si>
+  <si>
+    <t>197.0, 57.5</t>
+  </si>
+  <si>
+    <t>202.8, 40.2</t>
+  </si>
+  <si>
+    <t>222.6, 62.4</t>
+  </si>
+  <si>
+    <t>246.1, 52.4</t>
+  </si>
+  <si>
+    <t>263.9, 57.3</t>
+  </si>
+  <si>
+    <t>262.2, 91.9</t>
+  </si>
+  <si>
+    <t>236.8, 109.3</t>
+  </si>
+  <si>
+    <t>282.0, 110.4</t>
+  </si>
+  <si>
+    <t>372.5, 112.6</t>
+  </si>
+  <si>
+    <t>413.9, 132.3</t>
+  </si>
+  <si>
+    <t>424.0, 158.2</t>
+  </si>
+  <si>
+    <t>443.7, 163.1</t>
+  </si>
+  <si>
+    <t>363.4, 199.1</t>
+  </si>
+  <si>
+    <t>129.1, 35.4</t>
+  </si>
+  <si>
+    <t>178.0, 50.8</t>
+  </si>
+  <si>
+    <t>189.9, 60.8</t>
+  </si>
+  <si>
+    <t>216.9, 46.0</t>
+  </si>
+  <si>
+    <t>248.3, 59.9</t>
+  </si>
+  <si>
+    <t>244.5, 64.5</t>
+  </si>
+  <si>
+    <t>260.3, 80.1</t>
+  </si>
+  <si>
+    <t>366.9, 45.4</t>
+  </si>
+  <si>
+    <t>446.1, 126.1</t>
+  </si>
+  <si>
+    <t>Lahav</t>
+  </si>
+  <si>
+    <t>392.1, 121.4</t>
+  </si>
+  <si>
+    <t>423.4, 167.5</t>
+  </si>
+  <si>
+    <t>408.4, 183.7</t>
+  </si>
+  <si>
+    <t>358.7, 213.0</t>
+  </si>
+  <si>
+    <t>534.7, 162.0</t>
+  </si>
+  <si>
+    <t>530.2, 154.3</t>
+  </si>
+  <si>
+    <t>604.6, 168.0</t>
+  </si>
+  <si>
+    <t>627.9, 121.8</t>
+  </si>
+  <si>
+    <t>766.4, 182.4</t>
+  </si>
+  <si>
+    <t>Matta</t>
+  </si>
+  <si>
+    <t>590.9, 327.1</t>
+  </si>
+  <si>
+    <t>622.2, 320.8</t>
+  </si>
+  <si>
+    <t>626.1, 420.8</t>
+  </si>
+  <si>
+    <t>694.6, 420.8</t>
+  </si>
+  <si>
+    <t>821.7, 331.3</t>
+  </si>
+  <si>
+    <t>532.2, 420.8</t>
+  </si>
+  <si>
+    <t>588.9, 458.3</t>
+  </si>
+  <si>
+    <t>498.9, 522.9</t>
+  </si>
+  <si>
+    <t>880.4, 622.9</t>
+  </si>
+  <si>
+    <t>Ramat Hanadiv</t>
+  </si>
+  <si>
+    <t>467.6, 162.5</t>
+  </si>
+  <si>
+    <t>521.8, 167.9</t>
+  </si>
+  <si>
+    <t>562.3, 196.4</t>
+  </si>
+  <si>
+    <t>510.1, 209.8</t>
+  </si>
+  <si>
+    <t>515.4, 213.4</t>
+  </si>
+  <si>
+    <t>656.9, 215.2</t>
+  </si>
+  <si>
+    <t>677.8, 212.5</t>
+  </si>
+  <si>
+    <t>717.4, 163.4</t>
+  </si>
+  <si>
+    <t>834.6, 175.9</t>
+  </si>
+  <si>
+    <t>556.4, 284.8</t>
+  </si>
+  <si>
+    <t>Ofer</t>
+  </si>
+  <si>
+    <t>309.1, 287.4</t>
+  </si>
+  <si>
+    <t>331.0, 327.1</t>
+  </si>
+  <si>
+    <t>309.4, 348.2</t>
+  </si>
+  <si>
+    <t>361.9, 409.1</t>
+  </si>
+  <si>
+    <t>457.3, 350.9</t>
+  </si>
+  <si>
+    <t>481.1, 329.7</t>
+  </si>
+  <si>
+    <t>489.3, 245.0</t>
+  </si>
+  <si>
+    <t>557.1, 319.1</t>
+  </si>
+  <si>
+    <t>498.8, 401.2</t>
+  </si>
+  <si>
+    <t>516.3, 419.7</t>
+  </si>
+  <si>
+    <t>566.4, 440.9</t>
+  </si>
+  <si>
+    <t>594.8, 472.6</t>
+  </si>
+  <si>
+    <t>647.2, 517.6</t>
+  </si>
+  <si>
+    <t>662.1, 456.8</t>
+  </si>
+  <si>
+    <t>666.1, 380.0</t>
+  </si>
+  <si>
+    <t>760.6, 602.4</t>
+  </si>
+  <si>
+    <t>Karei Deshe</t>
+  </si>
+  <si>
+    <t>470.1, 164.8</t>
+  </si>
+  <si>
+    <t>665.7, 164.8</t>
+  </si>
+  <si>
+    <t>778.2, 218.0</t>
+  </si>
+  <si>
+    <t>838.0, 246.2</t>
+  </si>
+  <si>
+    <t>786.3, 292.0</t>
+  </si>
+  <si>
+    <t>741.3, 324.6</t>
+  </si>
+  <si>
+    <t>661.6, 368.9</t>
+  </si>
+  <si>
+    <t>940.7, 340.8</t>
+  </si>
+  <si>
+    <t>1107.2, 259.5</t>
+  </si>
+  <si>
+    <t>Yechiam</t>
+  </si>
+  <si>
+    <t>625.8, 75.9</t>
+  </si>
+  <si>
+    <t>695.7, 75.9</t>
+  </si>
+  <si>
+    <t>525.2, 115.0</t>
+  </si>
+  <si>
+    <t>584.9, 131.5</t>
+  </si>
+  <si>
+    <t>532.7, 141.0</t>
+  </si>
+  <si>
+    <t>546.8, 149.3</t>
+  </si>
+  <si>
+    <t>659.5, 200.2</t>
+  </si>
+  <si>
+    <t>663.1, 209.6</t>
+  </si>
+  <si>
+    <t>718.5, 178.9</t>
+  </si>
+  <si>
+    <t>725.7, 193.1</t>
+  </si>
+  <si>
+    <t>768.0, 214.4</t>
+  </si>
+  <si>
+    <t>838.4, 242.8</t>
+  </si>
+  <si>
+    <t>789.7, 259.3</t>
+  </si>
+  <si>
+    <t>960.0, 204.9</t>
+  </si>
+  <si>
+    <t>871.5, 142.2</t>
+  </si>
+  <si>
+    <t>836.1, 113.8</t>
+  </si>
+  <si>
+    <t>870.5, 84.2</t>
+  </si>
+  <si>
+    <t>979.3, 113.8</t>
+  </si>
+  <si>
+    <t>1069.6, 79.5</t>
+  </si>
+  <si>
+    <t>1272.8, 115.0</t>
+  </si>
+  <si>
+    <t>En Ya'aqov</t>
+  </si>
+  <si>
+    <t>MeanKgHa</t>
+  </si>
+  <si>
+    <t>Lower_CL</t>
+  </si>
+  <si>
+    <t>Upper_CL</t>
+  </si>
+  <si>
+    <t>DPM_cm</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>n</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -136,8 +980,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,9 +1306,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5867ED9-0939-4D5B-B25F-BAD49DCE1AE4}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -469,7 +1322,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -483,7 +1336,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -497,7 +1350,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -511,7 +1364,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -525,7 +1378,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -539,7 +1392,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -561,13 +1414,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE42270F-7848-40EB-8D12-35C95CD62807}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.06640625" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -584,7 +1437,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -601,7 +1454,7 @@
         <v>487.3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -618,7 +1471,7 @@
         <v>312.8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -635,7 +1488,7 @@
         <v>201.6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -652,7 +1505,7 @@
         <v>157.9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -669,7 +1522,7 @@
         <v>395.7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -686,7 +1539,7 @@
         <v>373.9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -703,7 +1556,7 @@
         <v>306.3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -720,7 +1573,7 @@
         <v>251.7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -737,7 +1590,7 @@
         <v>249.6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -754,7 +1607,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -771,7 +1624,7 @@
         <v>157.9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -788,7 +1641,7 @@
         <v>138.30000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -805,7 +1658,7 @@
         <v>197.2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -822,7 +1675,7 @@
         <v>136.1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -839,7 +1692,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -856,7 +1709,7 @@
         <v>64.099999999999994</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -873,7 +1726,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -890,7 +1743,7 @@
         <v>218.7</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -907,7 +1760,7 @@
         <v>122.4</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -924,7 +1777,7 @@
         <v>77.099999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -941,7 +1794,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -956,6 +1809,2246 @@
       </c>
       <c r="E23">
         <v>73.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204B0EE4-D5C3-405F-BF31-146618C97132}">
+  <dimension ref="A1:C67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" t="s">
+        <v>71</v>
+      </c>
+      <c r="C48" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>90</v>
+      </c>
+      <c r="B50" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>90</v>
+      </c>
+      <c r="B53" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55" t="s">
+        <v>77</v>
+      </c>
+      <c r="C55" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>90</v>
+      </c>
+      <c r="B56" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>90</v>
+      </c>
+      <c r="B58" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>90</v>
+      </c>
+      <c r="B59" t="s">
+        <v>81</v>
+      </c>
+      <c r="C59" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>90</v>
+      </c>
+      <c r="B60" t="s">
+        <v>82</v>
+      </c>
+      <c r="C60" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>90</v>
+      </c>
+      <c r="B61" t="s">
+        <v>83</v>
+      </c>
+      <c r="C61" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>90</v>
+      </c>
+      <c r="B62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>90</v>
+      </c>
+      <c r="B63" t="s">
+        <v>85</v>
+      </c>
+      <c r="C63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" t="s">
+        <v>86</v>
+      </c>
+      <c r="C64" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" t="s">
+        <v>87</v>
+      </c>
+      <c r="C65" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>90</v>
+      </c>
+      <c r="B66" t="s">
+        <v>88</v>
+      </c>
+      <c r="C66" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>90</v>
+      </c>
+      <c r="B67" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E548DDDD-2D2A-4DAB-8A7D-9E1F9335EA5D}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1982</v>
+      </c>
+      <c r="B2">
+        <v>349</v>
+      </c>
+      <c r="C2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1983</v>
+      </c>
+      <c r="B3">
+        <v>376</v>
+      </c>
+      <c r="C3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1984</v>
+      </c>
+      <c r="B4">
+        <v>132</v>
+      </c>
+      <c r="C4">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1985</v>
+      </c>
+      <c r="B5">
+        <v>297</v>
+      </c>
+      <c r="C5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1986</v>
+      </c>
+      <c r="B6">
+        <v>317</v>
+      </c>
+      <c r="C6">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1987</v>
+      </c>
+      <c r="B7">
+        <v>250</v>
+      </c>
+      <c r="C7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1988</v>
+      </c>
+      <c r="B8">
+        <v>408</v>
+      </c>
+      <c r="C8">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1989</v>
+      </c>
+      <c r="B9">
+        <v>488</v>
+      </c>
+      <c r="C9">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1990</v>
+      </c>
+      <c r="B10">
+        <v>326</v>
+      </c>
+      <c r="C10">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1991</v>
+      </c>
+      <c r="B11">
+        <v>407</v>
+      </c>
+      <c r="C11">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85CF35E-E9EC-4B64-A53F-BE268068634B}">
+  <dimension ref="A1:B119"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B18" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>182</v>
+      </c>
+      <c r="B20" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B21" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>184</v>
+      </c>
+      <c r="B22" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>184</v>
+      </c>
+      <c r="B23" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>184</v>
+      </c>
+      <c r="B25" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>184</v>
+      </c>
+      <c r="B26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>184</v>
+      </c>
+      <c r="B28" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>184</v>
+      </c>
+      <c r="B30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>184</v>
+      </c>
+      <c r="B37" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>210</v>
+      </c>
+      <c r="B38" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>210</v>
+      </c>
+      <c r="B39" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>210</v>
+      </c>
+      <c r="B40" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>210</v>
+      </c>
+      <c r="B41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>210</v>
+      </c>
+      <c r="B42" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>210</v>
+      </c>
+      <c r="B43" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>210</v>
+      </c>
+      <c r="B44" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>210</v>
+      </c>
+      <c r="B45" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>210</v>
+      </c>
+      <c r="B46" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>220</v>
+      </c>
+      <c r="B47" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>220</v>
+      </c>
+      <c r="B48" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>220</v>
+      </c>
+      <c r="B49" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>220</v>
+      </c>
+      <c r="B50" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>220</v>
+      </c>
+      <c r="B52" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>220</v>
+      </c>
+      <c r="B53" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>220</v>
+      </c>
+      <c r="B54" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>220</v>
+      </c>
+      <c r="B55" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>230</v>
+      </c>
+      <c r="B56" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>230</v>
+      </c>
+      <c r="B57" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>230</v>
+      </c>
+      <c r="B58" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>230</v>
+      </c>
+      <c r="B59" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>230</v>
+      </c>
+      <c r="B60" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>230</v>
+      </c>
+      <c r="B61" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>230</v>
+      </c>
+      <c r="B62" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>230</v>
+      </c>
+      <c r="B63" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>230</v>
+      </c>
+      <c r="B64" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>241</v>
+      </c>
+      <c r="B65" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>241</v>
+      </c>
+      <c r="B66" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>241</v>
+      </c>
+      <c r="B67" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>241</v>
+      </c>
+      <c r="B68" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>241</v>
+      </c>
+      <c r="B69" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>241</v>
+      </c>
+      <c r="B70" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>241</v>
+      </c>
+      <c r="B71" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>241</v>
+      </c>
+      <c r="B72" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>241</v>
+      </c>
+      <c r="B73" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>241</v>
+      </c>
+      <c r="B74" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>258</v>
+      </c>
+      <c r="B75" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>258</v>
+      </c>
+      <c r="B76" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>258</v>
+      </c>
+      <c r="B77" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>258</v>
+      </c>
+      <c r="B78" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>258</v>
+      </c>
+      <c r="B79" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>258</v>
+      </c>
+      <c r="B80" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>258</v>
+      </c>
+      <c r="B81" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>258</v>
+      </c>
+      <c r="B82" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>258</v>
+      </c>
+      <c r="B83" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>258</v>
+      </c>
+      <c r="B84" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>258</v>
+      </c>
+      <c r="B85" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>258</v>
+      </c>
+      <c r="B86" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>258</v>
+      </c>
+      <c r="B87" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>258</v>
+      </c>
+      <c r="B88" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>258</v>
+      </c>
+      <c r="B89" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>258</v>
+      </c>
+      <c r="B90" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>268</v>
+      </c>
+      <c r="B91" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>268</v>
+      </c>
+      <c r="B92" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>268</v>
+      </c>
+      <c r="B93" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>268</v>
+      </c>
+      <c r="B94" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>268</v>
+      </c>
+      <c r="B95" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>268</v>
+      </c>
+      <c r="B96" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>268</v>
+      </c>
+      <c r="B97" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>268</v>
+      </c>
+      <c r="B98" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>268</v>
+      </c>
+      <c r="B99" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>289</v>
+      </c>
+      <c r="B100" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>289</v>
+      </c>
+      <c r="B101" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>289</v>
+      </c>
+      <c r="B102" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>289</v>
+      </c>
+      <c r="B103" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>289</v>
+      </c>
+      <c r="B104" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>289</v>
+      </c>
+      <c r="B105" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>289</v>
+      </c>
+      <c r="B106" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>289</v>
+      </c>
+      <c r="B107" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>289</v>
+      </c>
+      <c r="B108" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>289</v>
+      </c>
+      <c r="B109" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>289</v>
+      </c>
+      <c r="B110" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>289</v>
+      </c>
+      <c r="B111" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>289</v>
+      </c>
+      <c r="B112" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>289</v>
+      </c>
+      <c r="B113" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>289</v>
+      </c>
+      <c r="B114" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>289</v>
+      </c>
+      <c r="B115" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>289</v>
+      </c>
+      <c r="B116" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>289</v>
+      </c>
+      <c r="B117" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>289</v>
+      </c>
+      <c r="B118" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>289</v>
+      </c>
+      <c r="B119" t="s">
+        <v>288</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D9D77E-4871-4962-BF00-003B2A0DCFA5}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1282.5999999999999</v>
+      </c>
+      <c r="C2" s="3">
+        <v>485.2</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2080</v>
+      </c>
+      <c r="E2" s="3">
+        <v>28.98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1583</v>
+      </c>
+      <c r="C3" s="3">
+        <v>790.6</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2375.3000000000002</v>
+      </c>
+      <c r="E3" s="3">
+        <v>23.34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1883.3</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1091.8</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2674.9</v>
+      </c>
+      <c r="E4" s="3">
+        <v>19.59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2183.6999999999998</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1388.8</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2978.6</v>
+      </c>
+      <c r="E5" s="3">
+        <v>16.97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2484.1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1681.8</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3286.4</v>
+      </c>
+      <c r="E6" s="3">
+        <v>15.06</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2784.4</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1970.7</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3598.2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>13.63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3">
+        <v>3084.8</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2255.6999999999998</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3913.9</v>
+      </c>
+      <c r="E8" s="3">
+        <v>12.53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>3385.2</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2537.1999999999998</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4233.2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>11.68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3">
+        <v>3685.5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2815.2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4555.8999999999996</v>
+      </c>
+      <c r="E10" s="3">
+        <v>11.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3">
+        <v>5187.3999999999996</v>
+      </c>
+      <c r="C11" s="3">
+        <v>4163.3999999999996</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6211.4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>20</v>
+      </c>
+      <c r="B12" s="3">
+        <v>6689.2</v>
+      </c>
+      <c r="C12" s="3">
+        <v>5462.4</v>
+      </c>
+      <c r="D12" s="3">
+        <v>7916.1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>8.5500000000000007</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>25</v>
+      </c>
+      <c r="B13" s="3">
+        <v>8191.1</v>
+      </c>
+      <c r="C13" s="3">
+        <v>6732.6</v>
+      </c>
+      <c r="D13" s="3">
+        <v>9649.5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>30</v>
+      </c>
+      <c r="B14" s="3">
+        <v>9692.9</v>
+      </c>
+      <c r="C14" s="3">
+        <v>7985.7</v>
+      </c>
+      <c r="D14" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E14" s="3">
+        <v>8.2100000000000009</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>35</v>
+      </c>
+      <c r="B15" s="3">
+        <v>11195</v>
+      </c>
+      <c r="C15" s="3">
+        <v>9228.2000000000007</v>
+      </c>
+      <c r="D15" s="3">
+        <v>13161</v>
+      </c>
+      <c r="E15" s="3">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3">
+        <v>12697</v>
+      </c>
+      <c r="C16" s="3">
+        <v>10464</v>
+      </c>
+      <c r="D16" s="3">
+        <v>14930</v>
+      </c>
+      <c r="E16" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>45</v>
+      </c>
+      <c r="B17" s="3">
+        <v>14198</v>
+      </c>
+      <c r="C17" s="3">
+        <v>11695</v>
+      </c>
+      <c r="D17" s="3">
+        <v>16702</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8.2200000000000006</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED47721A-256B-4817-921A-098973287BEA}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3">
+        <v>7.5071000000000003</v>
+      </c>
+      <c r="C2" s="3">
+        <v>75.66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>50</v>
+      </c>
+      <c r="B3" s="3">
+        <v>3.7536</v>
+      </c>
+      <c r="C3" s="3">
+        <v>37.83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>75</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2.5024000000000002</v>
+      </c>
+      <c r="C4" s="3">
+        <v>25.22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>100</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1.8768</v>
+      </c>
+      <c r="C5" s="3">
+        <v>18.920000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>150</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1.2512000000000001</v>
+      </c>
+      <c r="C6" s="3">
+        <v>12.61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>200</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.93840000000000001</v>
+      </c>
+      <c r="C7" s="3">
+        <v>9.4600000000000009</v>
       </c>
     </row>
   </sheetData>
